--- a/data/trans_dic/IP16A07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A07-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir</t>
+          <t>Menores que consumiero pastillas para dormir (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,6</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,1</t>
+          <t>0,0; 19,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,02</t>
+          <t>0,0; 9,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,9</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,77</t>
+          <t>0,0; 36,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,39</t>
+          <t>0,0; 18,82</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,48</t>
+          <t>0,31; 3,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,8</t>
+          <t>0,16; 1,59</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero pastillas para dormir (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4445</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4382</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3845</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3191</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3110</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2923</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2947</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3731</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3282</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>545; 6682</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0; 3937</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>576; 5737</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A07-Provincia-trans_dic.xlsx
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 6,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 4,3</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,9</t>
+          <t>0,0; 16,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,23</t>
+          <t>0,0; 11,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 11,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,32</t>
+          <t>0,0; 40,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,82</t>
+          <t>0,0; 17,06</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,76</t>
+          <t>0,28; 3,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,15; 1,58</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4445</t>
+          <t>0; 4388</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4382</t>
+          <t>0; 4784</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3845</t>
+          <t>0; 3173</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3191</t>
+          <t>0; 4012</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3110</t>
+          <t>0; 3379</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 2923</t>
+          <t>0; 2849</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 2947</t>
+          <t>0; 3247</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 3731</t>
+          <t>0; 3380</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 3282</t>
+          <t>0; 3768</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>545; 6682</t>
+          <t>497; 5750</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0; 3937</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>576; 5737</t>
+          <t>555; 5688</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A07-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A07-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron pastillas para dormir (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,3</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
     </row>
@@ -1074,27 +1074,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>3,4%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,61</t>
+          <t>0,0; 10,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,06</t>
+          <t>0,0; 15,93</t>
         </is>
       </c>
     </row>
@@ -1774,29 +1774,29 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,37; 4,28</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,58</t>
+          <t>0,18; 2,1</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero pastillas para dormir (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron pastillas para dormir (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2296,27 +2296,27 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>867</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>867</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4388</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4458</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 4784</t>
+          <t>0; 4331</t>
         </is>
       </c>
     </row>
@@ -2702,27 +2702,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2770,27 +2770,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>656</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3173</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2724</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4012</t>
+          <t>0; 3463</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -3336,27 +3336,27 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>541</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>541</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3379</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2439</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 2849</t>
+          <t>0; 3482</t>
         </is>
       </c>
     </row>
@@ -3544,27 +3544,27 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>653</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>654</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3247</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2939</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 3380</t>
+          <t>0; 3081</t>
         </is>
       </c>
     </row>
@@ -3742,37 +3742,37 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3810,29 +3810,29 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2061</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0; 3768</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>497; 5750</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3255</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>528; 6121</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0; 3038</t>
+          <t>0; 3462</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>555; 5688</t>
+          <t>549; 6470</t>
         </is>
       </c>
     </row>
